--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6331.55</v>
+        <v>6293.61</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5170.24</v>
+        <v>5228.06</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7276.48</v>
+        <v>7304.05</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5209.15</v>
+        <v>5247.96</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3231.4</v>
+        <v>3199.17</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6331.55</v>
+        <v>6268.41</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3123.49</v>
+        <v>3116.4</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2423.82</v>
+        <v>2417.83</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>26544.93</v>
+        <v>26629.42</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4207.36</v>
+        <v>4256.71</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8327.379999999999</v>
+        <v>8412.059999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4894.97</v>
+        <v>4940.88</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5137.35</v>
+        <v>5064.44</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7993.58</v>
+        <v>7944.02</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3367.6</v>
+        <v>3382.89</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3103.62</v>
+        <v>3162.62</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2473.74</v>
+        <v>2529.53</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4894.97</v>
+        <v>4928.77</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5788.08</v>
+        <v>5828.04</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5548.6</v>
+        <v>5586.91</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2530.34</v>
+        <v>2496.64</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5216.38</v>
+        <v>5146.9</v>
       </c>
     </row>
     <row r="24">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3235.21</v>
+        <v>3192.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>608-7589-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7904.67</v>
+        <v>5446.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2444.98</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>608-7505-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4324.79</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>617807-3629-CM26</t>
+          <t>608-7505-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2444.98</v>
+        <v>4240.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>608-7589-CM26</t>
+          <t>617807-3629-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5554.84</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2492.56</v>
+        <v>2502.26</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6398.63</v>
+        <v>6412.27</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>47450.7</v>
+        <v>47347.46</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4358.79</v>
+        <v>4288.45</v>
       </c>
     </row>
     <row r="34">
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>25594.53</v>
+        <v>25296.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>898-2497-CM26</t>
+          <t>1704-4096-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2585.87</v>
+        <v>16072.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1704-4096-CM26</t>
+          <t>898-2497-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,7 +2643,68 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>16151.69</v>
+        <v>2573.16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1704-4716-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>14610.7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1551,7 +1551,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3191-3050-CM26</t>
+          <t>3191-3021-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4928.77</v>
+        <v>5828.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3191-3021-CM26</t>
+          <t>617807-3551-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5828.04</v>
+        <v>5586.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>617807-3551-CM26</t>
+          <t>3191-3050-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5586.91</v>
+        <v>4928.77</v>
       </c>
     </row>
     <row r="22">
@@ -1978,7 +1978,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>617807-3629-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>7749.94</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>608-7505-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2397.13</v>
+        <v>4240.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>608-7505-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4240.14</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>617807-3629-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2397.13</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="30">
@@ -2527,7 +2527,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1704-4096-CM26</t>
+          <t>898-2497-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>16072.28</v>
+        <v>2573.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>898-2497-CM26</t>
+          <t>1704-4096-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2573.16</v>
+        <v>16072.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704-4716-CM26</t>
+          <t>898-2537-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,6 +2704,921 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
+        <v>50906.49</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>898-2538-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.602.126-5</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>60435.32</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>608-7804-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>73426.92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>608-7790-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>13755.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>608-7765-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>62150.78</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>608-9464-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>3529.14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>608-9183-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>7190.38</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3191-4246-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.102.017-1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>6571.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3191-4011-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.102.017-1</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>10841.87</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>608-9546-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>15152.15</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>608-9697-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>2743.25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>608-9704-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ARENYS MED S.A.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>6932.29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1422830-158-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>8462.15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1422830-162-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>4325.22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1422824-2750-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>7546.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1704-4716-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
         <v>14610.7</v>
       </c>
     </row>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>608-7589-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5446.11</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>617807-3629-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1998,17 +1998,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2100,7 +2100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>617807-3629-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>608-7589-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7749.94</v>
+        <v>5446.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4967-1297-CM26</t>
+          <t>3191-3081-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2502.26</v>
+        <v>18897.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3191-3409-CM26</t>
+          <t>4967-1297-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6412.27</v>
+        <v>2502.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>608-7752-CM26</t>
+          <t>3191-3409-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>47347.46</v>
+        <v>6412.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>608-7408-CM26</t>
+          <t>608-7752-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4288.45</v>
+        <v>47347.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3191-3857-CM26</t>
+          <t>608-7408-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>25296.72</v>
+        <v>4288.45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>898-2497-CM26</t>
+          <t>3191-3857-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2573.16</v>
+        <v>25296.72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1704-4096-CM26</t>
+          <t>898-2497-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,17 +2608,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>16072.28</v>
+        <v>2573.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>898-2537-CM26</t>
+          <t>1704-4096-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2659,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>50906.49</v>
+        <v>16072.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>898-2538-CM26</t>
+          <t>898-2537-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>60435.32</v>
+        <v>50906.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>608-7804-CM26</t>
+          <t>898-2538-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>73426.92</v>
+        <v>60435.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>608-7790-CM26</t>
+          <t>608-7765-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>13755.7</v>
+        <v>62150.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>608-7765-CM26</t>
+          <t>608-7790-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>62150.78</v>
+        <v>13755.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>608-9464-CM26</t>
+          <t>608-7804-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3529.14</v>
+        <v>73426.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>608-9183-CM26</t>
+          <t>608-9464-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7190.38</v>
+        <v>3529.14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3191-4246-CM26</t>
+          <t>608-9183-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>77.535.386-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6571.1</v>
+        <v>7190.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3191-4011-CM26</t>
+          <t>3191-4246-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10841.87</v>
+        <v>6571.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>608-9546-CM26</t>
+          <t>1422830-158-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15152.15</v>
+        <v>8462.15</v>
       </c>
     </row>
     <row r="47">
@@ -3381,7 +3381,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1422830-158-CM26</t>
+          <t>3191-4011-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8462.15</v>
+        <v>10841.87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1422830-162-CM26</t>
+          <t>608-9546-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4325.22</v>
+        <v>15152.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1422824-2750-CM26</t>
+          <t>1422830-162-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7546.6</v>
+        <v>4325.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1704-4716-CM26</t>
+          <t>1422824-2750-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3584,17 +3584,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,7 +3619,800 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
+        <v>7546.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1704-4716-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
         <v>14610.7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>608-9958-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>2651.81</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1422824-2800-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>2947.59</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1422824-2915-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TECNIKA S A</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>4416.89</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1422830-169-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>NEUMANN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>78.936.310-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>6255.76</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>617807-4871-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.602.036-6</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>7653.58</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>608-10990-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>AETICA SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>2942.39</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1422830-176-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>68109.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3191-5020-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>61.102.017-1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>7103.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1704-5313-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>9990.07</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>608-11665-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>2870.44</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>608-11651-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.606.602-1</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>18524.55</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1704-5419-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>12474.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
@@ -623,7 +623,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1790,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2831,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3140,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3327,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4063,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -762,7 +766,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>875646-1692-CM26</t>
+          <t>1422830-120-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -782,17 +786,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.602.057-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -802,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -821,13 +825,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3199.17</v>
+        <v>6268.41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1422830-120-CM26</t>
+          <t>875646-1692-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -847,17 +851,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.602.057-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -867,22 +871,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6268.41</v>
+        <v>3199.17</v>
       </c>
     </row>
     <row r="8">
@@ -936,7 +944,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1058,7 +1070,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1180,7 +1196,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1383,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1448,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1513,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1668,7 +1700,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1807,7 +1843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3191-3135-CM26</t>
+          <t>3191-3137-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1827,7 +1863,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1862,13 +1898,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5146.9</v>
+        <v>3192.12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3191-3137-CM26</t>
+          <t>3191-3135-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1888,7 +1924,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1923,7 +1959,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3192.12</v>
+        <v>5146.9</v>
       </c>
     </row>
     <row r="25">
@@ -1990,7 +2026,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>608-7505-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2030,12 +2066,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2045,13 +2081,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2397.13</v>
+        <v>4240.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>608-7505-CM26</t>
+          <t>617807-3629-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2071,17 +2107,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2091,28 +2127,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4240.14</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>617807-3629-CM26</t>
+          <t>608-7589-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2132,17 +2172,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2152,12 +2192,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2167,13 +2207,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2397.13</v>
+        <v>5446.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>608-7589-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2213,22 +2253,26 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>5446.11</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="30">
@@ -2404,7 +2448,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2465,7 +2513,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2639,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2722,7 +2778,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>898-2537-CM26</t>
+          <t>898-2538-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2742,7 +2798,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2762,28 +2818,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>50906.49</v>
+        <v>60435.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>898-2538-CM26</t>
+          <t>898-2537-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2803,7 +2863,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2823,32 +2883,28 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>60435.32</v>
+        <v>50906.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>608-7765-CM26</t>
+          <t>608-7804-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2888,12 +2944,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2903,7 +2959,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>62150.78</v>
+        <v>73426.92</v>
       </c>
     </row>
     <row r="41">
@@ -2970,7 +3026,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>608-7804-CM26</t>
+          <t>608-7765-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3010,22 +3066,26 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>73426.92</v>
+        <v>62150.78</v>
       </c>
     </row>
     <row r="43">
@@ -3218,7 +3278,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1422830-158-CM26</t>
+          <t>608-9697-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3238,17 +3298,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3258,28 +3318,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8462.15</v>
+        <v>2743.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>608-9697-CM26</t>
+          <t>1422830-158-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3299,17 +3363,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3319,12 +3383,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3338,13 +3402,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2743.25</v>
+        <v>8462.15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>608-9704-CM26</t>
+          <t>3191-4011-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3364,17 +3428,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3384,12 +3448,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3399,13 +3463,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>6932.29</v>
+        <v>10841.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3191-4011-CM26</t>
+          <t>608-9546-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3425,17 +3489,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3445,12 +3509,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3460,13 +3524,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>10841.87</v>
+        <v>15152.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>608-9546-CM26</t>
+          <t>608-9704-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3506,12 +3570,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3521,7 +3585,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>15152.15</v>
+        <v>6932.29</v>
       </c>
     </row>
     <row r="51">
@@ -3575,7 +3639,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3852,7 +3920,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3913,7 +3981,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3974,7 +4042,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4035,7 +4103,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4141,7 +4209,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3191-5020-CM26</t>
+          <t>1704-5313-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4161,17 +4229,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4181,12 +4249,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4196,13 +4264,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>7103.7</v>
+        <v>9990.07</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1704-5313-CM26</t>
+          <t>3191-5020-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4222,17 +4290,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4242,12 +4310,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4257,7 +4325,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9990.07</v>
+        <v>7103.7</v>
       </c>
     </row>
     <row r="63">
@@ -4372,7 +4440,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4477,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4441,6 +4513,441 @@
       </c>
       <c r="M65" s="2" t="n">
         <v>12474.87</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3191-5332-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.102.017-1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>7564.72</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3191-5330-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.102.017-1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>5730.27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3191-5329-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.102.017-1</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>5730.27</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1422830-185-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>4044.66</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1422830-191-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.602.054-4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TARGET SITE CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>66826.35000000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1704-5886-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>6215.59</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1704-5917-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>25121.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
+++ b/docs/oc-regiones/endoprotesis-ortopedia-y-trauma/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1422830-120-CM26</t>
+          <t>875646-1692-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.602.057-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>79.744.580-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>6268.41</v>
+        <v>3199.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>875646-1692-CM26</t>
+          <t>1422830-120-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -851,17 +851,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.602.057-9</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3199.17</v>
+        <v>6268.41</v>
       </c>
     </row>
     <row r="8">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3191-3021-CM26</t>
+          <t>617807-3551-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1631,28 +1631,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5828.04</v>
+        <v>5586.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>617807-3551-CM26</t>
+          <t>3191-3050-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1677,12 +1681,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1692,32 +1696,28 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5586.91</v>
+        <v>4928.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3191-3050-CM26</t>
+          <t>3191-3021-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4928.77</v>
+        <v>5828.04</v>
       </c>
     </row>
     <row r="22">
@@ -1843,7 +1843,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3191-3137-CM26</t>
+          <t>3191-3135-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3192.12</v>
+        <v>5146.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3191-3135-CM26</t>
+          <t>3191-3137-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5146.9</v>
+        <v>3192.12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>608-7409-CM26</t>
+          <t>608-7503-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2005,22 +2005,26 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7749.94</v>
+        <v>2397.13</v>
       </c>
     </row>
     <row r="26">
@@ -2172,7 +2176,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2213,7 +2217,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>608-7503-CM26</t>
+          <t>608-7409-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2233,7 +2237,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2253,26 +2257,22 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2397.13</v>
+        <v>7749.94</v>
       </c>
     </row>
     <row r="30">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>898-2497-CM26</t>
+          <t>1704-4096-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2573.16</v>
+        <v>16072.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1704-4096-CM26</t>
+          <t>898-2497-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2772,13 +2772,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>16072.28</v>
+        <v>2573.16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>898-2538-CM26</t>
+          <t>898-2537-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2818,32 +2818,28 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>60435.32</v>
+        <v>50906.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>898-2537-CM26</t>
+          <t>898-2538-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2863,7 +2859,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2883,28 +2879,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>50906.49</v>
+        <v>60435.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>608-7804-CM26</t>
+          <t>608-7765-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2944,22 +2944,26 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>73426.92</v>
+        <v>62150.78</v>
       </c>
     </row>
     <row r="41">
@@ -3026,7 +3030,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>608-7765-CM26</t>
+          <t>608-7804-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3066,26 +3070,22 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>62150.78</v>
+        <v>73426.92</v>
       </c>
     </row>
     <row r="43">
@@ -3278,7 +3278,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>608-9697-CM26</t>
+          <t>1422830-158-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3298,17 +3298,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2743.25</v>
+        <v>8462.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1422830-158-CM26</t>
+          <t>3191-4011-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3383,32 +3383,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8462.15</v>
+        <v>10841.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3191-4011-CM26</t>
+          <t>608-9697-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3433,12 +3429,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3448,28 +3444,32 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10841.87</v>
+        <v>2743.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>608-9546-CM26</t>
+          <t>608-9704-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3524,13 +3524,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>15152.15</v>
+        <v>6932.29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>608-9704-CM26</t>
+          <t>608-9546-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6932.29</v>
+        <v>15152.15</v>
       </c>
     </row>
     <row r="51">
@@ -3778,7 +3778,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>608-9958-CM26</t>
+          <t>1422824-2800-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3803,12 +3803,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3833,13 +3833,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2651.81</v>
+        <v>2947.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1422824-2800-CM26</t>
+          <t>608-9958-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2947.59</v>
+        <v>2651.81</v>
       </c>
     </row>
     <row r="56">
@@ -4766,7 +4766,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1422830-191-CM26</t>
+          <t>898-3528-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4806,12 +4806,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4821,13 +4821,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>66826.35000000001</v>
+        <v>5332.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1704-5886-CM26</t>
+          <t>1422830-191-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4882,71 +4882,132 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>6215.59</v>
+        <v>66826.35000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>1704-5886-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.606.608-0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>6215.59</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>1704-5917-CM26</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>61.606.608-0</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>TRIMED CHILE SPA</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n">
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
         <v>25121.26</v>
       </c>
     </row>
